--- a/参会人员名单.xlsx
+++ b/参会人员名单.xlsx
@@ -77,7 +77,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,13 +90,6 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -435,12 +428,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -543,82 +551,82 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
@@ -627,10 +635,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
@@ -639,10 +647,10 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
@@ -651,10 +659,10 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
@@ -663,10 +671,10 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
@@ -675,10 +683,10 @@
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
@@ -687,26 +695,29 @@
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1040,54 +1051,55 @@
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
